--- a/site/exports/xjtu-management-industrial-operations.xlsx
+++ b/site/exports/xjtu-management-industrial-operations.xlsx
@@ -795,7 +795,7 @@
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr"/>
